--- a/data/gaming/masterdata/gaming_masterdata_260411.xlsx
+++ b/data/gaming/masterdata/gaming_masterdata_260411.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\gaming\masterdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{554A60AA-4A45-4DD8-A8B8-629AC8BDC8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD5F9D1-8AAA-4059-8D85-A62B2DD9978D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="158">
   <si>
     <t>id</t>
   </si>
@@ -106,41 +106,22 @@
   </si>
   <si>
     <t>쿠팡</t>
-  </si>
-  <si>
-    <t>window</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9018633339?itemId=26440741094&amp;vendorItemId=93416362417</t>
   </si>
   <si>
     <t>쿠팡</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>LOQ 15AHP10, R7 250/5060</t>
-  </si>
-  <si>
     <t>gpu</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>리전 5 15AHP10, R7 260/5060</t>
-  </si>
-  <si>
     <t>리전 5 15AKP10, R7 350/5070</t>
   </si>
   <si>
     <t>오멘 16, R7 350/5060</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/9277699361?itemId=27465445395&amp;vendorItemId=94430699317</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8837462423?itemId=25754178542&amp;vendorItemId=92742426422</t>
-  </si>
-  <si>
     <t>오멘 16, R9 8940HX/5060</t>
   </si>
   <si>
@@ -148,13 +129,6 @@
   </si>
   <si>
     <t>TUF A14, R7 350/5060</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8952675716?itemId=26188751314&amp;vendorItemId=93168176760</t>
-  </si>
-  <si>
-    <t>single</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>1TB</t>
@@ -165,94 +139,18 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8774172630?itemId=25524523223&amp;vendorItemId=92516319080</t>
-  </si>
-  <si>
     <t>TUF A16, R7 260/5060</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8783926143?itemId=25559511189&amp;vendorItemId=92550827920</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8853447738?itemId=25811877071&amp;vendorItemId=92799026566</t>
-  </si>
-  <si>
     <t>TUF A16, R7 260/5050</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8775686288?itemId=25530075131&amp;vendorItemId=92521813430</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8835024384?itemId=25745774086&amp;vendorItemId=92734130287</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8982779083?itemId=26301942628&amp;vendorItemId=93279668232</t>
-  </si>
-  <si>
     <t>TUF A16, R9 8940HX/5070 WQXGA</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/9167902430?itemId=27014590927&amp;vendorItemId=93983227395</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8899002146?itemId=25984595201&amp;vendorItemId=92967046632</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8773992950?itemId=25523735423&amp;vendorItemId=92515547957</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9205272622?itemId=27183962156&amp;vendorItemId=94151511891</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9074269633?itemId=26652309626&amp;vendorItemId=93624824750</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8904297554?itemId=26003982478&amp;vendorItemId=92986077906</t>
-  </si>
-  <si>
     <t>니트로 V 16 슬림, R7 260/5060</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8971714769?itemId=26258100341&amp;vendorItemId=93236465468</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8880588148?itemId=25917512831&amp;vendorItemId=92903064695</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9234391064?itemId=27300437532&amp;vendorItemId=94266985637</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9200481145?itemId=27164469297&amp;vendorItemId=94132178204</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8733078928?itemId=25376712122&amp;vendorItemId=92370774835</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8733078928?itemId=25777643455&amp;vendorItemId=92765623467</t>
-  </si>
-  <si>
-    <t>win11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8873266044?itemId=25890522816&amp;vendorItemId=92876445013</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8836980191?itemId=25752060438&amp;vendorItemId=92740350838</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8935925393?itemId=25890522454&amp;vendorItemId=92876444744</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8760962623?itemId=25474920787&amp;vendorItemId=92467342021</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8792486494?itemId=25592949982&amp;vendorItemId=92583699379</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8790276970?itemId=25584164030&amp;vendorItemId=92575058855</t>
-  </si>
-  <si>
     <t>오멘 맥스 16, R9 375HX/5060</t>
   </si>
   <si>
@@ -265,21 +163,6 @@
     <t>오멘 맥스 16, U9 275HX/5070 Ti</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8966522013?itemId=26241074138&amp;vendorItemId=93219739755</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9325824364?itemId=27736313139&amp;vendorItemId=94697490099</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8715362832?itemId=25312533063&amp;vendorItemId=92307623157</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8771764425?itemId=25515886631&amp;vendorItemId=92507808343</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8941557079?itemId=26148695560&amp;vendorItemId=93128696273</t>
-  </si>
-  <si>
     <t>오멘 17, R7 350/5060</t>
   </si>
   <si>
@@ -292,21 +175,9 @@
     <t>레이더 A18, R9 9955HX/5080</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8686463967?itemId=25217316659&amp;vendorItemId=92213738237</t>
-  </si>
-  <si>
     <t>TUF A16, R7 260/5060 WQXGA</t>
   </si>
   <si>
-    <t>TUF F16, I7 14650HX/5060 WQXGA</t>
-  </si>
-  <si>
-    <t>TUF F16, I7 14650HX/5070 WQXGA</t>
-  </si>
-  <si>
-    <t>TUF F16, I5 14450HX/5050</t>
-  </si>
-  <si>
     <t>TUF A18, R7 260/5050</t>
   </si>
   <si>
@@ -331,24 +202,12 @@
     <t>니트로 18, R7 350/5070</t>
   </si>
   <si>
-    <t>빅터스 16, I5 13500HX/4060</t>
-  </si>
-  <si>
-    <t>빅터스 16, I5 14450HX/4060</t>
-  </si>
-  <si>
-    <t>소드 GF76 17.3, I7 14650HX/5060</t>
-  </si>
-  <si>
     <t>리전 7 16IAX10, U9 275HX/5070</t>
   </si>
   <si>
     <t>ROG 스트릭스 G18, U9 275HX/5070</t>
   </si>
   <si>
-    <t>오멘 15, I5 14450HX/5060</t>
-  </si>
-  <si>
     <t>벡터 16, U7 275HX/5080</t>
   </si>
   <si>
@@ -365,63 +224,12 @@
   </si>
   <si>
     <t>벡터 16, U7 275HX/5070 Ti</t>
-  </si>
-  <si>
-    <t>variant</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8826112134?itemId=25719163101&amp;vendorItemId=92707939317</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/7685542307?itemId=19025582401&amp;vendorItemId=86149803397</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8677554106?itemId=25190830588&amp;vendorItemId=92187575667</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8825969244?itemId=25789822919&amp;vendorItemId=92777600085</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8835398704?itemId=25746757768&amp;vendorItemId=92735093516</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8711669095?itemId=26764774488&amp;vendorItemId=93735603813</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASUS</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>acer</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>msi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lenovo</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>리전 프로 7 16IAX10, U9 275HX/5080</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>리전 프로 5 16IAX10, U9 275HX/5070</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>쿠팡</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -430,81 +238,25 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8771136679?itemId=25513329531&amp;vendorItemId=92505305899</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8826133206?itemId=25719248433&amp;vendorItemId=92708022379</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8763580498?itemId=25484221675&amp;vendorItemId=92476480219</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8758944787?itemId=25467752802&amp;vendorItemId=92460264359</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8771223830?itemId=25513732236&amp;vendorItemId=92505701532</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>portability</t>
-  </si>
-  <si>
-    <t>display</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>cpu_style</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>single</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROG 스트릭스 G16, R9 9955HX3D/5070 Ti</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>single</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8721382195?itemId=25333537099&amp;vendorItemId=92328320231</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>dual</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8852815391?itemId=25809161282&amp;vendorItemId=92796439383</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>onboard</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8899002151?itemId=25984595232&amp;vendorItemId=92967046664</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>weight</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>battery</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>리전 프로 7 16IAX10, U9 275HX/5070 Ti</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>오멘 맥스 16, U7 255HX/5060 OLED</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -513,16 +265,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/9007205840?itemId=27375892821&amp;vendorItemId=94341787823</t>
-  </si>
-  <si>
-    <t>LG</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/9254540096?itemId=27375892823&amp;vendorItemId=94341787824</t>
-  </si>
-  <si>
     <t>lg</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -531,57 +273,288 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/9395836180?itemId=27904531391&amp;vendorItemId=94863309099</t>
-  </si>
-  <si>
     <t>블랙</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>에어로 X16, R7 350/5060</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그램프로 16, U5 225H/5050</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그램프로 17, U5 225H/5050</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>16GB 램</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>32GB 램</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>on_crawl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리도스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>screen_type</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>variant</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>display</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8966522013?itemid=26241074138&amp;vendoritemid=93219739755</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/7685542307?itemid=19025582401&amp;vendoritemid=86149803397</t>
+  </si>
+  <si>
+    <t>빅터스 16, i5 13500HX/4060</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9167902430?itemid=27014590927&amp;vendoritemid=93983227395</t>
+  </si>
+  <si>
+    <t>TUF F16, i5 14450HX/5050</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8677554106?itemid=25190830588&amp;vendoritemid=92187575667</t>
+  </si>
+  <si>
+    <t>빅터스 16, i5 14450HX/4060</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9325824364?itemid=27736313139&amp;vendoritemid=94697490099</t>
+  </si>
+  <si>
+    <t>오멘 15, i5 14450HX/5060</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8835024384?itemid=25745774086&amp;vendoritemid=92734130287</t>
+  </si>
+  <si>
+    <t>TUF F16, i7 14650HX/5060 WQXGA</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8982779083?itemid=26301942628&amp;vendoritemid=93279668232</t>
+  </si>
+  <si>
+    <t>TUF F16, i7 14650HX/5070 WQXGA</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8825969244?itemid=25789822919&amp;vendoritemid=92777600085</t>
+  </si>
+  <si>
+    <t>msi</t>
+  </si>
+  <si>
+    <t>소드 GF76 17.3, i7 14650HX/5060</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9018633339?itemid=26440741094&amp;vendoritemid=93416362417</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9205272622?itemid=27183962156&amp;vendoritemid=94151511891</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8852815391?itemid=25809161282&amp;vendoritemid=92796439383</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8952675716?itemid=26188751314&amp;vendoritemid=93168176760</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8853447738?itemid=25811877071&amp;vendoritemid=92799026566</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8774172630?itemid=25524523223&amp;vendoritemid=92516319080</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8783926143?itemid=25559511189&amp;vendoritemid=92550827920</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8899002146?itemid=25984595201&amp;vendoritemid=92967046632</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8773992950?itemid=25523735423&amp;vendoritemid=92515547957</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8835398704?itemid=25746757768&amp;vendoritemid=92735093516</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9074269633?itemid=26652309626&amp;vendoritemid=93624824750</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9234391064?itemid=27300437532&amp;vendoritemid=94266985637</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9200481145?itemid=27164469297&amp;vendoritemid=94132178204</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8899002151?itemid=25984595232&amp;vendoritemid=92967046664</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8826112134?itemid=25719163101&amp;vendoritemid=92707939317</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8941557079?itemid=26148695560&amp;vendoritemid=93128696273</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8771136679?itemid=25513329531&amp;vendoritemid=92505305899</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8826133206?itemid=25719248433&amp;vendoritemid=92708022379</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8763580498?itemid=25484221675&amp;vendoritemid=92476480219</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8775686288?itemid=25530075131&amp;vendoritemid=92521813430</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8837462423?itemid=25754178542&amp;vendoritemid=92742426422</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8711669095?itemid=26764774488&amp;vendoritemid=93735603813</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8733078928?itemid=25376712122&amp;vendoritemid=92370774835</t>
+  </si>
+  <si>
+    <t>ROG 스트릭스 G16, R9 9955HX3D/5070 Ti</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8733078928?itemid=25777643455&amp;vendoritemid=92765623467</t>
+  </si>
+  <si>
+    <t>win11</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9277699361?itemid=27465445395&amp;vendoritemid=94430699317</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8771764425?itemid=25515886631&amp;vendoritemid=92507808343</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8715362832?itemid=25312533063&amp;vendoritemid=92307623157</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8904297554?itemid=26003982478&amp;vendoritemid=92986077906</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8880588148?itemid=25917512831&amp;vendoritemid=92903064695</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8882397835?itemid=25923808163&amp;vendoritemid=92909249701</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8971714769?itemid=26258100341&amp;vendoritemid=93236465468</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8721382195?itemid=25333537099&amp;vendoritemid=92328320231</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8790276970?itemid=25584164030&amp;vendoritemid=92575058855</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8792486494?itemid=25592949982&amp;vendoritemid=92583699379</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8758944787?itemid=25467752802&amp;vendoritemid=92460264359</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8771223830?itemid=25513732236&amp;vendoritemid=92505701532</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8935925393?itemid=25890522454&amp;vendoritemid=92876444744</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8836980191?itemid=25752060438&amp;vendoritemid=92740350838</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8873266044?itemid=25890522816&amp;vendoritemid=92876445013</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8686463967?itemid=25217316659&amp;vendoritemid=92213738237</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8760962623?itemid=25474920787&amp;vendoritemid=92467342021</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9007205840?itemid=27375892821&amp;vendoritemid=94341787823</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9254540096?itemid=27375892823&amp;vendoritemid=94341787824</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9395836180?itemid=27904531391&amp;vendoritemid=94863309099</t>
+  </si>
+  <si>
+    <t>gigabyte</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8938802218?itemid=26137504736&amp;vendoritemid=93117664782</t>
+  </si>
+  <si>
+    <t>리전 프로 5 16IAX10, U9 275HX/5070</t>
+  </si>
+  <si>
+    <t>리전 프로 7 16IAX10, U9 275HX/5080</t>
+  </si>
+  <si>
+    <t>리전 프로 7 16IAX10, U9 275HX/5070 Ti</t>
+  </si>
+  <si>
+    <t>asus</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>LOQ 15Ahp10, R7 250/5060</t>
+  </si>
+  <si>
+    <t>리전 5 15Ahp10, R7 260/5060</t>
+  </si>
+  <si>
+    <t>lenovo</t>
+  </si>
+  <si>
     <t>gigabyte</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>에어로 X16, R7 350/5060</t>
+    <t>dual</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>그램프로 16, U5 225H/5050</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그램프로 17, U5 225H/5050</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8938802218?itemId=26137504736&amp;vendorItemId=93117664782</t>
-  </si>
-  <si>
-    <t>16GB 램</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>32GB 램</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>on_crawl</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리도스</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>is_active</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8882397835?itemId=25923808163&amp;vendorItemId=92909249701</t>
-  </si>
-  <si>
-    <t>screen_type</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>https://www.coupang.com/vp/products/8960448289</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/9018648022</t>
   </si>
 </sst>
 </file>
@@ -1605,16 +1578,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="I1" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
         <v>6</v>
@@ -1629,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="N1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O1" t="s">
         <v>10</v>
@@ -1641,28 +1614,28 @@
         <v>12</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="S1" t="s">
         <v>13</v>
       </c>
       <c r="T1" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="U1" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="W1" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="Y1" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="AA1" t="s">
         <v>14</v>
@@ -1673,13 +1646,13 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1687,28 +1660,31 @@
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>210</v>
+      </c>
       <c r="M2" t="str">
-        <f t="shared" ref="M2:M33" si="0">TRIM(MID(D2, FIND(",", D2)+1, FIND("/", D2)-FIND(",", D2)-1))</f>
-        <v>U7 255HX</v>
+        <f>TRIM(MID(D2, FIND(",", D2)+1, FIND("/", D2)-FIND(",", D2)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N2" t="str">
-        <f t="shared" ref="N2:N33" si="1">_xlfn.LET(
+        <f>_xlfn.LET(
     _xlpm.txt, TRIM(MID(D2, FIND("/", D2)+1, LEN(D2))),
     IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
 )</f>
-        <v>5060</v>
+        <v>5070</v>
       </c>
       <c r="O2">
         <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="Q2">
         <v>1024</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="str" cm="1">
         <f t="array" ref="S2">IFERROR(
@@ -1718,27 +1694,27 @@
         <v>16</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
-        <v>103</v>
+      <c r="B3" t="s">
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1746,22 +1722,28 @@
       <c r="I3">
         <v>1</v>
       </c>
+      <c r="J3">
+        <v>180</v>
+      </c>
       <c r="M3" t="str">
-        <f t="shared" si="0"/>
-        <v>I5 13500HX</v>
+        <f>TRIM(MID(D3, FIND(",", D3)+1, FIND("/", D3)-FIND(",", D3)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" si="1"/>
-        <v>4060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D3, FIND("/", D3)+1, LEN(D3))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P3" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="Q3">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1771,30 +1753,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D3), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1802,22 +1784,28 @@
       <c r="I4">
         <v>1</v>
       </c>
+      <c r="J4">
+        <v>200</v>
+      </c>
       <c r="M4" t="str">
-        <f t="shared" si="0"/>
-        <v>I5 14450HX</v>
+        <f>TRIM(MID(D4, FIND(",", D4)+1, FIND("/", D4)-FIND(",", D4)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N4" t="str">
-        <f t="shared" si="1"/>
-        <v>5050</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D4, FIND("/", D4)+1, LEN(D4))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P4" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="Q4">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1827,30 +1815,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D4), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1858,19 +1846,25 @@
       <c r="I5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>135</v>
+      </c>
       <c r="M5" t="str">
-        <f t="shared" si="0"/>
-        <v>I5 14450HX</v>
+        <f>TRIM(MID(D5, FIND(",", D5)+1, FIND("/", D5)-FIND(",", D5)-1))</f>
+        <v>R7 260</v>
       </c>
       <c r="N5" t="str">
-        <f t="shared" si="1"/>
-        <v>4060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D5, FIND("/", D5)+1, LEN(D5))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O5">
         <v>16</v>
       </c>
       <c r="P5" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q5">
         <v>512</v>
@@ -1883,30 +1877,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D5), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1914,19 +1908,25 @@
       <c r="I6">
         <v>1</v>
       </c>
+      <c r="J6">
+        <v>210</v>
+      </c>
       <c r="M6" t="str">
-        <f t="shared" si="0"/>
-        <v>I5 14450HX</v>
+        <f>TRIM(MID(D6, FIND(",", D6)+1, FIND("/", D6)-FIND(",", D6)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D6, FIND("/", D6)+1, LEN(D6))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="Q6">
         <v>1024</v>
@@ -1939,30 +1939,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D6), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1970,22 +1970,28 @@
       <c r="I7">
         <v>1</v>
       </c>
+      <c r="J7">
+        <v>230</v>
+      </c>
       <c r="M7" t="str">
-        <f t="shared" si="0"/>
-        <v>I7 14650HX</v>
+        <f>TRIM(MID(D7, FIND(",", D7)+1, FIND("/", D7)-FIND(",", D7)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N7" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D7, FIND("/", D7)+1, LEN(D7))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P7" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="Q7">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1995,30 +2001,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D7), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2026,22 +2032,28 @@
       <c r="I8">
         <v>1</v>
       </c>
+      <c r="J8">
+        <v>270</v>
+      </c>
       <c r="M8" t="str">
-        <f t="shared" si="0"/>
-        <v>I7 14650HX</v>
+        <f>TRIM(MID(D8, FIND(",", D8)+1, FIND("/", D8)-FIND(",", D8)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N8" t="str">
-        <f t="shared" si="1"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D8, FIND("/", D8)+1, LEN(D8))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="Q8">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2051,30 +2063,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D8), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>1</v>
       </c>
       <c r="AA8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2082,22 +2094,28 @@
       <c r="I9">
         <v>1</v>
       </c>
+      <c r="J9">
+        <v>285</v>
+      </c>
       <c r="M9" t="str">
-        <f t="shared" si="0"/>
-        <v>I7 14650HX</v>
+        <f>TRIM(MID(D9, FIND(",", D9)+1, FIND("/", D9)-FIND(",", D9)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N9" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D9, FIND("/", D9)+1, LEN(D9))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O9">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P9" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="Q9">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2107,7 +2125,7 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D9), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -2118,25 +2136,25 @@
       <c r="W9">
         <v>1</v>
       </c>
-      <c r="X9">
-        <v>270</v>
-      </c>
-      <c r="Y9">
-        <v>75</v>
-      </c>
       <c r="AA9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>121</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2144,51 +2162,67 @@
       <c r="I10">
         <v>1</v>
       </c>
+      <c r="J10">
+        <v>280</v>
+      </c>
       <c r="M10" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 250</v>
+        <f>TRIM(MID(D10, FIND(",", D10)+1, FIND("/", D10)-FIND(",", D10)-1))</f>
+        <v>R9 9955HX3D</v>
       </c>
       <c r="N10" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D10, FIND("/", D10)+1, LEN(D10))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O10">
         <v>16</v>
       </c>
       <c r="P10" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="Q10">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
-      <c r="S10">
-        <v>15.6</v>
+      <c r="S10" t="str" cm="1">
+        <f t="array" ref="S10">IFERROR(
+    LOOKUP(2^15, SEARCH({"16","18","14"}, D10), {"16","18","14"}),
+    ""
+)</f>
+        <v>16</v>
       </c>
       <c r="U10">
         <v>2</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2196,22 +2230,28 @@
       <c r="I11">
         <v>1</v>
       </c>
+      <c r="J11">
+        <v>285</v>
+      </c>
       <c r="M11" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 260</v>
+        <f>TRIM(MID(D11, FIND(",", D11)+1, FIND("/", D11)-FIND(",", D11)-1))</f>
+        <v>R9 9955HX3D</v>
       </c>
       <c r="N11" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D11, FIND("/", D11)+1, LEN(D11))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O11">
         <v>16</v>
       </c>
       <c r="P11" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="Q11">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2224,33 +2264,27 @@
         <v>16</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
-        <v>130</v>
+      <c r="B12" t="s">
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2258,22 +2292,28 @@
       <c r="I12">
         <v>1</v>
       </c>
+      <c r="J12">
+        <v>400</v>
+      </c>
       <c r="M12" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 260</v>
+        <f>TRIM(MID(D12, FIND(",", D12)+1, FIND("/", D12)-FIND(",", D12)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N12" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D12, FIND("/", D12)+1, LEN(D12))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5080</v>
       </c>
       <c r="O12">
         <v>32</v>
       </c>
       <c r="P12" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="Q12">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -2283,36 +2323,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D12), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -2320,19 +2354,25 @@
       <c r="I13">
         <v>1</v>
       </c>
+      <c r="J13">
+        <v>240</v>
+      </c>
       <c r="M13" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 260</v>
+        <f>TRIM(MID(D13, FIND(",", D13)+1, FIND("/", D13)-FIND(",", D13)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N13" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D13, FIND("/", D13)+1, LEN(D13))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O13">
         <v>32</v>
       </c>
       <c r="P13" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="Q13">
         <v>1024</v>
@@ -2345,30 +2385,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D13), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -2376,22 +2416,28 @@
       <c r="I14">
         <v>1</v>
       </c>
+      <c r="J14">
+        <v>285</v>
+      </c>
       <c r="M14" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 260</v>
+        <f>TRIM(MID(D14, FIND(",", D14)+1, FIND("/", D14)-FIND(",", D14)-1))</f>
+        <v>U9 275HX</v>
       </c>
       <c r="N14" t="str">
-        <f t="shared" si="1"/>
-        <v>5050</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D14, FIND("/", D14)+1, LEN(D14))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O14">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P14" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="Q14">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2401,30 +2447,36 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D14), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>34</v>
+      <c r="B15" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -2432,19 +2484,25 @@
       <c r="I15">
         <v>1</v>
       </c>
+      <c r="J15">
+        <v>198</v>
+      </c>
       <c r="M15" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(MID(D15, FIND(",", D15)+1, FIND("/", D15)-FIND(",", D15)-1))</f>
         <v>R7 260</v>
       </c>
       <c r="N15" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D15, FIND("/", D15)+1, LEN(D15))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O15">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P15" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="Q15">
         <v>512</v>
@@ -2457,30 +2515,36 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D15), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U15">
+        <v>9</v>
+      </c>
+      <c r="V15">
         <v>6</v>
       </c>
-      <c r="V15">
-        <v>4</v>
-      </c>
       <c r="W15">
         <v>0</v>
       </c>
       <c r="AA15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2488,22 +2552,28 @@
       <c r="I16">
         <v>1</v>
       </c>
+      <c r="J16">
+        <v>205</v>
+      </c>
       <c r="M16" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(MID(D16, FIND(",", D16)+1, FIND("/", D16)-FIND(",", D16)-1))</f>
         <v>R7 260</v>
       </c>
       <c r="N16" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D16, FIND("/", D16)+1, LEN(D16))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O16">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P16" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="Q16">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2513,10 +2583,10 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D16), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -2525,18 +2595,18 @@
         <v>0</v>
       </c>
       <c r="AA16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>44</v>
+      <c r="B17" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -2544,22 +2614,28 @@
       <c r="I17">
         <v>1</v>
       </c>
+      <c r="J17">
+        <v>215</v>
+      </c>
       <c r="M17" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 260</v>
+        <f>TRIM(MID(D17, FIND(",", D17)+1, FIND("/", D17)-FIND(",", D17)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N17" t="str">
-        <f t="shared" si="1"/>
-        <v>5050</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D17, FIND("/", D17)+1, LEN(D17))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O17">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="Q17">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2569,30 +2645,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D17), {"16","18","14"}),
     ""
 )</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>0</v>
       </c>
       <c r="AA17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2600,19 +2676,25 @@
       <c r="I18">
         <v>1</v>
       </c>
+      <c r="J18">
+        <v>145</v>
+      </c>
       <c r="M18" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(MID(D18, FIND(",", D18)+1, FIND("/", D18)-FIND(",", D18)-1))</f>
         <v>R7 260</v>
       </c>
       <c r="N18" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D18, FIND("/", D18)+1, LEN(D18))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5050</v>
       </c>
       <c r="O18">
         <v>16</v>
       </c>
       <c r="P18" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="Q18">
         <v>512</v>
@@ -2625,10 +2707,10 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D18), {"16","18","14"}),
     ""
 )</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>4</v>
@@ -2637,18 +2719,18 @@
         <v>0</v>
       </c>
       <c r="AA18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -2656,19 +2738,25 @@
       <c r="I19">
         <v>1</v>
       </c>
+      <c r="J19">
+        <v>165</v>
+      </c>
       <c r="M19" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(MID(D19, FIND(",", D19)+1, FIND("/", D19)-FIND(",", D19)-1))</f>
         <v>R7 260</v>
       </c>
       <c r="N19" t="str">
-        <f t="shared" si="1"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D19, FIND("/", D19)+1, LEN(D19))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O19">
         <v>16</v>
       </c>
       <c r="P19" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="Q19">
         <v>512</v>
@@ -2681,10 +2769,10 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D19), {"16","18","14"}),
     ""
 )</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -2693,16 +2781,18 @@
         <v>0</v>
       </c>
       <c r="AA19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -2710,19 +2800,25 @@
       <c r="I20">
         <v>1</v>
       </c>
+      <c r="J20">
+        <v>170</v>
+      </c>
       <c r="M20" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(MID(D20, FIND(",", D20)+1, FIND("/", D20)-FIND(",", D20)-1))</f>
         <v>R7 260</v>
       </c>
       <c r="N20" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D20, FIND("/", D20)+1, LEN(D20))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O20">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P20" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="Q20">
         <v>512</v>
@@ -2730,31 +2826,35 @@
       <c r="R20">
         <v>0</v>
       </c>
-      <c r="S20">
-        <v>15.1</v>
+      <c r="S20" t="str" cm="1">
+        <f t="array" ref="S20">IFERROR(
+    LOOKUP(2^15, SEARCH({"16","18","14"}, D20), {"16","18","14"}),
+    ""
+)</f>
+        <v>16</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>0</v>
       </c>
       <c r="AA20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -2762,22 +2862,28 @@
       <c r="I21">
         <v>1</v>
       </c>
+      <c r="J21">
+        <v>190</v>
+      </c>
       <c r="M21" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D21, FIND(",", D21)+1, FIND("/", D21)-FIND(",", D21)-1))</f>
+        <v>R9 8940HX</v>
       </c>
       <c r="N21" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D21, FIND("/", D21)+1, LEN(D21))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5070</v>
       </c>
       <c r="O21">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="Q21">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2793,24 +2899,24 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2818,22 +2924,28 @@
       <c r="I22">
         <v>1</v>
       </c>
+      <c r="J22">
+        <v>160</v>
+      </c>
       <c r="M22" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D22, FIND(",", D22)+1, FIND("/", D22)-FIND(",", D22)-1))</f>
+        <v>R7 260</v>
       </c>
       <c r="N22" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D22, FIND("/", D22)+1, LEN(D22))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5050</v>
       </c>
       <c r="O22">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="Q22">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2849,24 +2961,24 @@
         <v>1</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W22">
         <v>0</v>
       </c>
       <c r="AA22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -2874,22 +2986,28 @@
       <c r="I23">
         <v>1</v>
       </c>
+      <c r="J23">
+        <v>180</v>
+      </c>
       <c r="M23" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D23, FIND(",", D23)+1, FIND("/", D23)-FIND(",", D23)-1))</f>
+        <v>R7 260</v>
       </c>
       <c r="N23" t="str">
-        <f t="shared" si="1"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D23, FIND("/", D23)+1, LEN(D23))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O23">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="Q23">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2905,24 +3023,24 @@
         <v>1</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W23">
         <v>0</v>
       </c>
       <c r="AA23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>132</v>
+      <c r="B24" t="s">
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2930,22 +3048,28 @@
       <c r="I24">
         <v>1</v>
       </c>
+      <c r="J24">
+        <v>200</v>
+      </c>
       <c r="M24" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D24, FIND(",", D24)+1, FIND("/", D24)-FIND(",", D24)-1))</f>
+        <v>R7 260</v>
       </c>
       <c r="N24" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D24, FIND("/", D24)+1, LEN(D24))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O24">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P24" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="Q24">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2955,13 +3079,13 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D24), {"16","18","14"}),
     ""
 )</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -2972,13 +3096,13 @@
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -2986,19 +3110,25 @@
       <c r="I25">
         <v>1</v>
       </c>
+      <c r="J25">
+        <v>140</v>
+      </c>
       <c r="M25" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D25, FIND(",", D25)+1, FIND("/", D25)-FIND(",", D25)-1))</f>
+        <v>i5 14450HX</v>
       </c>
       <c r="N25" t="str">
-        <f t="shared" si="1"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D25, FIND("/", D25)+1, LEN(D25))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5050</v>
       </c>
       <c r="O25">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P25" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q25">
         <v>512</v>
@@ -3011,16 +3141,16 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D25), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="s">
         <v>16</v>
@@ -3028,13 +3158,13 @@
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -3042,19 +3172,25 @@
       <c r="I26">
         <v>1</v>
       </c>
+      <c r="J26">
+        <v>165</v>
+      </c>
       <c r="M26" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D26, FIND(",", D26)+1, FIND("/", D26)-FIND(",", D26)-1))</f>
+        <v>i7 14650HX</v>
       </c>
       <c r="N26" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D26, FIND("/", D26)+1, LEN(D26))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O26">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P26" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q26">
         <v>512</v>
@@ -3062,31 +3198,35 @@
       <c r="R26">
         <v>0</v>
       </c>
-      <c r="S26">
-        <v>17.3</v>
+      <c r="S26" t="str" cm="1">
+        <f t="array" ref="S26">IFERROR(
+    LOOKUP(2^15, SEARCH({"16","18","14"}, D26), {"16","18","14"}),
+    ""
+)</f>
+        <v>14</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -3094,53 +3234,67 @@
       <c r="I27">
         <v>1</v>
       </c>
+      <c r="J27">
+        <v>185</v>
+      </c>
       <c r="M27" t="str">
-        <f t="shared" si="0"/>
-        <v>R7 350</v>
+        <f>TRIM(MID(D27, FIND(",", D27)+1, FIND("/", D27)-FIND(",", D27)-1))</f>
+        <v>i7 14650HX</v>
       </c>
       <c r="N27" t="str">
-        <f t="shared" si="1"/>
-        <v>5070 Ti</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D27, FIND("/", D27)+1, LEN(D27))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O27">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P27" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q27">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="str" cm="1">
         <f t="array" ref="S27">IFERROR(
     LOOKUP(2^15, SEARCH({"16","18","14"}, D27), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B28" s="1"/>
+      <c r="B28" t="s">
+        <v>143</v>
+      </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>68</v>
+      </c>
+      <c r="E28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -3148,37 +3302,49 @@
       <c r="I28">
         <v>1</v>
       </c>
+      <c r="J28">
+        <v>180</v>
+      </c>
       <c r="M28" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(MID(D28, FIND(",", D28)+1, FIND("/", D28)-FIND(",", D28)-1))</f>
         <v>R7 350</v>
       </c>
       <c r="N28" t="str">
-        <f t="shared" si="1"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D28, FIND("/", D28)+1, LEN(D28))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O28">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P28" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="Q28">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R28">
         <v>0</v>
       </c>
       <c r="S28">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="U28">
+        <v>8</v>
+      </c>
+      <c r="V28">
         <v>6</v>
       </c>
-      <c r="V28">
-        <v>8</v>
-      </c>
       <c r="W28">
         <v>0</v>
+      </c>
+      <c r="X28">
+        <v>190</v>
+      </c>
+      <c r="Y28">
+        <v>76</v>
       </c>
       <c r="AA28" t="s">
         <v>16</v>
@@ -3186,13 +3352,19 @@
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>68</v>
+      </c>
+      <c r="E29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -3200,55 +3372,59 @@
       <c r="I29">
         <v>1</v>
       </c>
+      <c r="J29">
+        <v>195</v>
+      </c>
       <c r="M29" t="str">
-        <f t="shared" si="0"/>
-        <v>R9 375HX</v>
-      </c>
-      <c r="N29" t="str">
-        <f t="shared" si="1"/>
+        <f>TRIM(MID(D29, FIND(",", D29)+1, FIND("/", D29)-FIND(",", D29)-1))</f>
+        <v>R7 350</v>
+      </c>
+      <c r="N29">
         <v>5060</v>
       </c>
       <c r="O29">
         <v>32</v>
       </c>
       <c r="P29" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="Q29">
         <v>512</v>
       </c>
       <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29" t="str" cm="1">
-        <f t="array" ref="S29">IFERROR(
-    LOOKUP(2^15, SEARCH({"16","18","14"}, D29), {"16","18","14"}),
-    ""
-)</f>
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>16</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>0</v>
       </c>
+      <c r="X29">
+        <v>190</v>
+      </c>
+      <c r="Y29">
+        <v>76</v>
+      </c>
       <c r="AA29" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>119</v>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -3256,25 +3432,31 @@
       <c r="I30">
         <v>1</v>
       </c>
+      <c r="J30">
+        <v>125</v>
+      </c>
       <c r="M30" t="str">
-        <f t="shared" si="0"/>
-        <v>R9 375HX</v>
+        <f>TRIM(MID(D30, FIND(",", D30)+1, FIND("/", D30)-FIND(",", D30)-1))</f>
+        <v>i5 13500HX</v>
       </c>
       <c r="N30" t="str">
-        <f t="shared" si="1"/>
-        <v>5080</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D30, FIND("/", D30)+1, LEN(D30))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>4060</v>
       </c>
       <c r="O30">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q30">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="str" cm="1">
         <f t="array" ref="S30">IFERROR(
@@ -3284,13 +3466,13 @@
         <v>16</v>
       </c>
       <c r="U30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="s">
         <v>16</v>
@@ -3298,13 +3480,13 @@
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -3312,19 +3494,25 @@
       <c r="I31">
         <v>1</v>
       </c>
+      <c r="J31">
+        <v>130</v>
+      </c>
       <c r="M31" t="str">
-        <f t="shared" si="0"/>
-        <v>R9 8940HX</v>
+        <f>TRIM(MID(D31, FIND(",", D31)+1, FIND("/", D31)-FIND(",", D31)-1))</f>
+        <v>i5 14450HX</v>
       </c>
       <c r="N31" t="str">
-        <f t="shared" si="1"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D31, FIND("/", D31)+1, LEN(D31))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>4060</v>
       </c>
       <c r="O31">
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="Q31">
         <v>512</v>
@@ -3337,13 +3525,13 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D31), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -3353,14 +3541,14 @@
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
-        <v>26</v>
+      <c r="B32" t="s">
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -3368,19 +3556,25 @@
       <c r="I32">
         <v>1</v>
       </c>
+      <c r="J32">
+        <v>180</v>
+      </c>
       <c r="M32" t="str">
-        <f t="shared" si="0"/>
-        <v>R9 8940HX</v>
+        <f>TRIM(MID(D32, FIND(",", D32)+1, FIND("/", D32)-FIND(",", D32)-1))</f>
+        <v>i5 14450HX</v>
       </c>
       <c r="N32" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D32, FIND("/", D32)+1, LEN(D32))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O32">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="P32" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q32">
         <v>1024</v>
@@ -3393,13 +3587,13 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D32), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>1</v>
@@ -3410,13 +3604,13 @@
     </row>
     <row r="33" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -3424,22 +3618,28 @@
       <c r="I33">
         <v>1</v>
       </c>
+      <c r="J33">
+        <v>200</v>
+      </c>
       <c r="M33" t="str">
-        <f t="shared" si="0"/>
-        <v>R9 9955HX</v>
+        <f>TRIM(MID(D33, FIND(",", D33)+1, FIND("/", D33)-FIND(",", D33)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N33" t="str">
-        <f t="shared" si="1"/>
-        <v>5080</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D33, FIND("/", D33)+1, LEN(D33))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O33">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P33" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q33">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3449,42 +3649,30 @@
     LOOKUP(2^15, SEARCH({"16","18","14"}, D33), {"16","18","14"}),
     ""
 )</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>1</v>
-      </c>
-      <c r="X33">
-        <v>360</v>
-      </c>
-      <c r="Y33">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>54</v>
+      <c r="B34" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -3492,22 +3680,25 @@
       <c r="I34">
         <v>1</v>
       </c>
+      <c r="J34">
+        <v>200</v>
+      </c>
       <c r="M34" t="str">
-        <f t="shared" ref="M34:M52" si="2">TRIM(MID(D34, FIND(",", D34)+1, FIND("/", D34)-FIND(",", D34)-1))</f>
-        <v>R9 9955HX3D</v>
+        <f>TRIM(MID(D34, FIND(",", D34)+1, FIND("/", D34)-FIND(",", D34)-1))</f>
+        <v>R9 8940HX</v>
       </c>
       <c r="N34" t="str">
-        <f t="shared" ref="N34:N56" si="3">_xlfn.LET(
+        <f>_xlfn.LET(
     _xlpm.txt, TRIM(MID(D34, FIND("/", D34)+1, LEN(D34))),
     IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
 )</f>
-        <v>5070 Ti</v>
+        <v>5060</v>
       </c>
       <c r="O34">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P34" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="Q34">
         <v>1024</v>
@@ -3523,10 +3714,10 @@
         <v>16</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>1</v>
@@ -3536,20 +3727,14 @@
       </c>
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>55</v>
+      <c r="B35" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -3557,19 +3742,25 @@
       <c r="I35">
         <v>1</v>
       </c>
+      <c r="J35">
+        <v>185</v>
+      </c>
       <c r="M35" t="str">
-        <f t="shared" si="2"/>
-        <v>R9 9955HX3D</v>
+        <f>TRIM(MID(D35, FIND(",", D35)+1, FIND("/", D35)-FIND(",", D35)-1))</f>
+        <v>U7 255H</v>
       </c>
       <c r="N35" t="str">
-        <f t="shared" si="3"/>
-        <v>5070 Ti</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D35, FIND("/", D35)+1, LEN(D35))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O35">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P35" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="Q35">
         <v>1024</v>
@@ -3585,27 +3776,27 @@
         <v>16</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>25</v>
+      <c r="B36" t="s">
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -3613,35 +3804,37 @@
       <c r="I36">
         <v>1</v>
       </c>
+      <c r="J36">
+        <v>210</v>
+      </c>
       <c r="M36" t="str">
-        <f t="shared" si="2"/>
-        <v>U7 255H</v>
+        <f>TRIM(MID(D36, FIND(",", D36)+1, FIND("/", D36)-FIND(",", D36)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N36" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D36, FIND("/", D36)+1, LEN(D36))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5060</v>
       </c>
       <c r="O36">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="P36" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="Q36">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R36">
         <v>0</v>
       </c>
-      <c r="S36" t="str" cm="1">
-        <f t="array" ref="S36">IFERROR(
-    LOOKUP(2^15, SEARCH({"16","18","14"}, D36), {"16","18","14"}),
-    ""
-)</f>
-        <v>16</v>
+      <c r="S36">
+        <v>17.3</v>
       </c>
       <c r="U36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -3655,13 +3848,13 @@
     </row>
     <row r="37" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -3669,25 +3862,31 @@
       <c r="I37">
         <v>1</v>
       </c>
+      <c r="J37">
+        <v>280</v>
+      </c>
       <c r="M37" t="str">
-        <f t="shared" si="2"/>
-        <v>U7 275HX</v>
+        <f>TRIM(MID(D37, FIND(",", D37)+1, FIND("/", D37)-FIND(",", D37)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N37" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D37, FIND("/", D37)+1, LEN(D37))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5070 Ti</v>
       </c>
       <c r="O37">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P37" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>1024</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="str" cm="1">
         <f t="array" ref="S37">IFERROR(
@@ -3700,16 +3899,10 @@
         <v>1</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>1</v>
-      </c>
-      <c r="X37">
-        <v>270</v>
-      </c>
-      <c r="Y37">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="s">
         <v>16</v>
@@ -3717,13 +3910,13 @@
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -3731,25 +3924,31 @@
       <c r="I38">
         <v>1</v>
       </c>
+      <c r="J38">
+        <v>230</v>
+      </c>
       <c r="M38" t="str">
-        <f t="shared" si="2"/>
-        <v>U7 275HX</v>
+        <f>TRIM(MID(D38, FIND(",", D38)+1, FIND("/", D38)-FIND(",", D38)-1))</f>
+        <v>R9 375HX</v>
       </c>
       <c r="N38" t="str">
-        <f t="shared" si="3"/>
-        <v>5080</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D38, FIND("/", D38)+1, LEN(D38))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O38">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P38" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q38">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="str" cm="1">
         <f t="array" ref="S38">IFERROR(
@@ -3759,19 +3958,13 @@
         <v>16</v>
       </c>
       <c r="U38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>1</v>
-      </c>
-      <c r="X38">
-        <v>270</v>
-      </c>
-      <c r="Y38">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="s">
         <v>16</v>
@@ -3779,13 +3972,13 @@
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -3793,25 +3986,31 @@
       <c r="I39">
         <v>1</v>
       </c>
+      <c r="J39">
+        <v>450</v>
+      </c>
       <c r="M39" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D39, FIND(",", D39)+1, FIND("/", D39)-FIND(",", D39)-1))</f>
+        <v>R9 375HX</v>
       </c>
       <c r="N39" t="str">
-        <f t="shared" si="3"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D39, FIND("/", D39)+1, LEN(D39))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5080</v>
       </c>
       <c r="O39">
         <v>32</v>
       </c>
       <c r="P39" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="Q39">
         <v>1024</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="str" cm="1">
         <f t="array" ref="S39">IFERROR(
@@ -3821,13 +4020,13 @@
         <v>16</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="s">
         <v>16</v>
@@ -3835,13 +4034,13 @@
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -3849,25 +4048,31 @@
       <c r="I40">
         <v>1</v>
       </c>
+      <c r="J40">
+        <v>250</v>
+      </c>
       <c r="M40" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D40, FIND(",", D40)+1, FIND("/", D40)-FIND(",", D40)-1))</f>
+        <v>U7 255HX</v>
       </c>
       <c r="N40" t="str">
-        <f t="shared" si="3"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D40, FIND("/", D40)+1, LEN(D40))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O40">
         <v>32</v>
       </c>
       <c r="P40" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="Q40">
         <v>1024</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="str" cm="1">
         <f t="array" ref="S40">IFERROR(
@@ -3877,10 +4082,10 @@
         <v>16</v>
       </c>
       <c r="U40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40">
         <v>1</v>
@@ -3891,13 +4096,13 @@
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -3905,25 +4110,31 @@
       <c r="I41">
         <v>1</v>
       </c>
+      <c r="J41">
+        <v>255</v>
+      </c>
       <c r="M41" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D41, FIND(",", D41)+1, FIND("/", D41)-FIND(",", D41)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N41" t="str">
-        <f t="shared" si="3"/>
-        <v>5070 Ti</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D41, FIND("/", D41)+1, LEN(D41))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O41">
         <v>32</v>
       </c>
       <c r="P41" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="Q41">
         <v>1024</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="str" cm="1">
         <f t="array" ref="S41">IFERROR(
@@ -3933,10 +4144,10 @@
         <v>16</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>1</v>
@@ -3947,13 +4158,13 @@
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -3961,38 +4172,44 @@
       <c r="I42">
         <v>1</v>
       </c>
+      <c r="J42">
+        <v>320</v>
+      </c>
       <c r="M42" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D42, FIND(",", D42)+1, FIND("/", D42)-FIND(",", D42)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N42" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D42, FIND("/", D42)+1, LEN(D42))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5070 Ti</v>
       </c>
       <c r="O42">
         <v>32</v>
       </c>
       <c r="P42" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="Q42">
         <v>1024</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="str" cm="1">
         <f t="array" ref="S42">IFERROR(
     LOOKUP(2^15, SEARCH({"16","18","14"}, D42), {"16","18","14"}),
     ""
 )</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U42">
         <v>1</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
         <v>1</v>
@@ -4003,13 +4220,13 @@
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -4017,55 +4234,57 @@
       <c r="I43">
         <v>1</v>
       </c>
+      <c r="J43">
+        <v>140</v>
+      </c>
       <c r="M43" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D43, FIND(",", D43)+1, FIND("/", D43)-FIND(",", D43)-1))</f>
+        <v>R7 250</v>
       </c>
       <c r="N43" t="str">
-        <f t="shared" si="3"/>
-        <v>5080</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D43, FIND("/", D43)+1, LEN(D43))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O43">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P43" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q43">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R43">
         <v>0</v>
       </c>
-      <c r="S43" t="str" cm="1">
-        <f t="array" ref="S43">IFERROR(
-    LOOKUP(2^15, SEARCH({"16","18","14"}, D43), {"16","18","14"}),
-    ""
-)</f>
-        <v>16</v>
+      <c r="S43">
+        <v>15.6</v>
       </c>
       <c r="U43">
         <v>2</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>62</v>
+      <c r="B44" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -4073,55 +4292,57 @@
       <c r="I44">
         <v>1</v>
       </c>
+      <c r="J44">
+        <v>178</v>
+      </c>
       <c r="M44" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D44, FIND(",", D44)+1, FIND("/", D44)-FIND(",", D44)-1))</f>
+        <v>R7 260</v>
       </c>
       <c r="N44" t="str">
-        <f t="shared" si="3"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D44, FIND("/", D44)+1, LEN(D44))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
       </c>
       <c r="O44">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="P44" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="Q44">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="R44">
         <v>0</v>
       </c>
-      <c r="S44" t="str" cm="1">
-        <f t="array" ref="S44">IFERROR(
-    LOOKUP(2^15, SEARCH({"16","18","14"}, D44), {"16","18","14"}),
-    ""
-)</f>
-        <v>18</v>
+      <c r="S44">
+        <v>15.1</v>
       </c>
       <c r="U44">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V44">
         <v>8</v>
       </c>
       <c r="W44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>61</v>
+      <c r="B45" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -4129,19 +4350,25 @@
       <c r="I45">
         <v>1</v>
       </c>
+      <c r="J45">
+        <v>225</v>
+      </c>
       <c r="M45" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D45, FIND(",", D45)+1, FIND("/", D45)-FIND(",", D45)-1))</f>
+        <v>R7 350</v>
       </c>
       <c r="N45" t="str">
-        <f t="shared" si="3"/>
-        <v>5070 Ti</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D45, FIND("/", D45)+1, LEN(D45))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O45">
         <v>32</v>
       </c>
       <c r="P45" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q45">
         <v>1024</v>
@@ -4149,21 +4376,17 @@
       <c r="R45">
         <v>0</v>
       </c>
-      <c r="S45" t="str" cm="1">
-        <f t="array" ref="S45">IFERROR(
-    LOOKUP(2^15, SEARCH({"16","18","14"}, D45), {"16","18","14"}),
-    ""
-)</f>
-        <v>18</v>
+      <c r="S45">
+        <v>15.1</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V45">
         <v>8</v>
       </c>
       <c r="W45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="s">
         <v>16</v>
@@ -4171,13 +4394,13 @@
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -4185,25 +4408,31 @@
       <c r="I46">
         <v>1</v>
       </c>
+      <c r="J46">
+        <v>330</v>
+      </c>
       <c r="M46" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D46, FIND(",", D46)+1, FIND("/", D46)-FIND(",", D46)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N46" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D46, FIND("/", D46)+1, LEN(D46))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5070</v>
       </c>
       <c r="O46">
         <v>32</v>
       </c>
       <c r="P46" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q46">
         <v>1024</v>
       </c>
       <c r="R46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="str" cm="1">
         <f t="array" ref="S46">IFERROR(
@@ -4213,10 +4442,10 @@
         <v>16</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V46">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W46">
         <v>1</v>
@@ -4227,13 +4456,13 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -4241,25 +4470,31 @@
       <c r="I47">
         <v>1</v>
       </c>
+      <c r="J47">
+        <v>245</v>
+      </c>
       <c r="M47" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D47, FIND(",", D47)+1, FIND("/", D47)-FIND(",", D47)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N47" t="str">
-        <f t="shared" si="3"/>
-        <v>5070 Ti</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D47, FIND("/", D47)+1, LEN(D47))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070</v>
       </c>
       <c r="O47">
         <v>32</v>
       </c>
       <c r="P47" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q47">
         <v>1024</v>
       </c>
       <c r="R47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="str" cm="1">
         <f t="array" ref="S47">IFERROR(
@@ -4269,13 +4504,19 @@
         <v>16</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W47">
         <v>1</v>
+      </c>
+      <c r="X47">
+        <v>243</v>
+      </c>
+      <c r="Y47">
+        <v>80</v>
       </c>
       <c r="AA47" t="s">
         <v>16</v>
@@ -4283,13 +4524,13 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -4297,19 +4538,25 @@
       <c r="I48">
         <v>1</v>
       </c>
+      <c r="J48">
+        <v>310</v>
+      </c>
       <c r="M48" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D48, FIND(",", D48)+1, FIND("/", D48)-FIND(",", D48)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N48" t="str">
-        <f t="shared" si="3"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D48, FIND("/", D48)+1, LEN(D48))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O48">
         <v>32</v>
       </c>
       <c r="P48" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q48">
         <v>1024</v>
@@ -4325,7 +4572,7 @@
         <v>16</v>
       </c>
       <c r="U48">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V48">
         <v>9</v>
@@ -4333,19 +4580,25 @@
       <c r="W48">
         <v>1</v>
       </c>
+      <c r="X48">
+        <v>243</v>
+      </c>
+      <c r="Y48">
+        <v>80</v>
+      </c>
       <c r="AA48" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -4353,19 +4606,25 @@
       <c r="I49">
         <v>1</v>
       </c>
+      <c r="J49">
+        <v>370</v>
+      </c>
       <c r="M49" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D49, FIND(",", D49)+1, FIND("/", D49)-FIND(",", D49)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N49" t="str">
-        <f t="shared" si="3"/>
-        <v>5070</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D49, FIND("/", D49)+1, LEN(D49))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
       </c>
       <c r="O49">
         <v>32</v>
       </c>
       <c r="P49" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q49">
         <v>1024</v>
@@ -4381,16 +4640,16 @@
         <v>16</v>
       </c>
       <c r="U49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W49">
         <v>1</v>
       </c>
       <c r="X49">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="Y49">
         <v>80</v>
@@ -4401,13 +4660,13 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -4415,19 +4674,25 @@
       <c r="I50">
         <v>1</v>
       </c>
+      <c r="J50">
+        <v>430</v>
+      </c>
       <c r="M50" t="str">
-        <f t="shared" si="2"/>
+        <f>TRIM(MID(D50, FIND(",", D50)+1, FIND("/", D50)-FIND(",", D50)-1))</f>
         <v>U9 275HX</v>
       </c>
       <c r="N50" t="str">
-        <f t="shared" si="3"/>
-        <v>5070 Ti</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D50, FIND("/", D50)+1, LEN(D50))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5080</v>
       </c>
       <c r="O50">
         <v>32</v>
       </c>
       <c r="P50" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="Q50">
         <v>1024</v>
@@ -4443,7 +4708,7 @@
         <v>16</v>
       </c>
       <c r="U50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V50">
         <v>9</v>
@@ -4452,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="X50">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="Y50">
         <v>80</v>
@@ -4463,13 +4728,13 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -4477,25 +4742,19 @@
       <c r="I51">
         <v>1</v>
       </c>
+      <c r="J51">
+        <v>270</v>
+      </c>
       <c r="M51" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D51, FIND(",", D51)+1, FIND("/", D51)-FIND(",", D51)-1))</f>
+        <v>U5 225H</v>
       </c>
       <c r="N51" t="str">
-        <f t="shared" si="3"/>
-        <v>5080</v>
-      </c>
-      <c r="O51">
-        <v>32</v>
-      </c>
-      <c r="P51" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q51">
-        <v>1024</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D51, FIND("/", D51)+1, LEN(D51))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5050</v>
       </c>
       <c r="S51" t="str" cm="1">
         <f t="array" ref="S51">IFERROR(
@@ -4505,19 +4764,19 @@
         <v>16</v>
       </c>
       <c r="U51">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="V51">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="Y51">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA51" t="s">
         <v>16</v>
@@ -4525,13 +4784,19 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>70</v>
+      </c>
+      <c r="E52" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -4539,47 +4804,41 @@
       <c r="I52">
         <v>1</v>
       </c>
+      <c r="J52">
+        <v>280</v>
+      </c>
       <c r="M52" t="str">
-        <f t="shared" si="2"/>
-        <v>U9 275HX</v>
+        <f>TRIM(MID(D52, FIND(",", D52)+1, FIND("/", D52)-FIND(",", D52)-1))</f>
+        <v>U5 225H</v>
       </c>
       <c r="N52" t="str">
-        <f t="shared" si="3"/>
-        <v>5070 Ti</v>
-      </c>
-      <c r="O52">
-        <v>32</v>
-      </c>
-      <c r="P52" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q52">
-        <v>1024</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D52, FIND("/", D52)+1, LEN(D52))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5050</v>
       </c>
       <c r="S52" t="str" cm="1">
         <f t="array" ref="S52">IFERROR(
     LOOKUP(2^15, SEARCH({"16","18","14"}, D52), {"16","18","14"}),
     ""
 )</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="V52">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="Y52">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA52" t="s">
         <v>16</v>
@@ -4587,13 +4846,19 @@
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="D53" t="s">
-        <v>147</v>
+        <v>70</v>
+      </c>
+      <c r="E53" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -4601,20 +4866,19 @@
       <c r="I53">
         <v>1</v>
       </c>
+      <c r="J53">
+        <v>280</v>
+      </c>
       <c r="M53" t="str">
-        <f t="shared" ref="M53:M55" si="4">TRIM(MID(D53, FIND(",", D53)+1, FIND("/", D53)-FIND(",", D53)-1))</f>
+        <f>TRIM(MID(D53, FIND(",", D53)+1, FIND("/", D53)-FIND(",", D53)-1))</f>
         <v>U5 225H</v>
       </c>
       <c r="N53" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D53, FIND("/", D53)+1, LEN(D53))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
         <v>5050</v>
-      </c>
-      <c r="S53" t="str" cm="1">
-        <f t="array" ref="S53">IFERROR(
-    LOOKUP(2^15, SEARCH({"16","18","14"}, D53), {"16","18","14"}),
-    ""
-)</f>
-        <v>16</v>
       </c>
       <c r="U53">
         <v>13</v>
@@ -4626,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="X53">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="Y53">
         <v>90</v>
@@ -4637,19 +4901,13 @@
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
-      </c>
-      <c r="E54" t="s">
-        <v>142</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -4657,35 +4915,53 @@
       <c r="I54">
         <v>1</v>
       </c>
+      <c r="J54">
+        <v>450</v>
+      </c>
       <c r="M54" t="str">
-        <f t="shared" si="4"/>
-        <v>U5 225H</v>
+        <f>TRIM(MID(D54, FIND(",", D54)+1, FIND("/", D54)-FIND(",", D54)-1))</f>
+        <v>R9 9955HX</v>
       </c>
       <c r="N54" t="str">
-        <f t="shared" si="3"/>
-        <v>5050</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D54, FIND("/", D54)+1, LEN(D54))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5080</v>
+      </c>
+      <c r="O54">
+        <v>16</v>
+      </c>
+      <c r="P54" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q54">
+        <v>1024</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
       </c>
       <c r="S54" t="str" cm="1">
         <f t="array" ref="S54">IFERROR(
     LOOKUP(2^15, SEARCH({"16","18","14"}, D54), {"16","18","14"}),
     ""
 )</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="U54">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V54">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="Y54">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AA54" t="s">
         <v>16</v>
@@ -4693,19 +4969,13 @@
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55" t="s">
-        <v>144</v>
-      </c>
-      <c r="F55">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -4713,25 +4983,50 @@
       <c r="I55">
         <v>1</v>
       </c>
+      <c r="J55">
+        <v>260</v>
+      </c>
       <c r="M55" t="str">
-        <f t="shared" si="4"/>
-        <v>U5 225H</v>
+        <f>TRIM(MID(D55, FIND(",", D55)+1, FIND("/", D55)-FIND(",", D55)-1))</f>
+        <v>U7 275HX</v>
       </c>
       <c r="N55" t="str">
-        <f t="shared" si="3"/>
-        <v>5050</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D55, FIND("/", D55)+1, LEN(D55))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5070 Ti</v>
+      </c>
+      <c r="O55">
+        <v>16</v>
+      </c>
+      <c r="P55" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q55">
+        <v>1024</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55" t="str" cm="1">
+        <f t="array" ref="S55">IFERROR(
+    LOOKUP(2^15, SEARCH({"16","18","14"}, D55), {"16","18","14"}),
+    ""
+)</f>
+        <v>16</v>
       </c>
       <c r="U55">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V55">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="Y55">
         <v>90</v>
@@ -4742,48 +5037,67 @@
     </row>
     <row r="56" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" t="s">
-        <v>150</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
         <v>1</v>
+      </c>
+      <c r="J56">
+        <v>330</v>
       </c>
       <c r="M56" t="str">
         <f>TRIM(MID(D56, FIND(",", D56)+1, FIND("/", D56)-FIND(",", D56)-1))</f>
-        <v>R7 350</v>
+        <v>U7 275HX</v>
       </c>
       <c r="N56" t="str">
-        <f t="shared" si="3"/>
-        <v>5060</v>
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D56, FIND("/", D56)+1, LEN(D56))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5080</v>
+      </c>
+      <c r="O56">
+        <v>16</v>
+      </c>
+      <c r="P56" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q56">
+        <v>1024</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56" t="str" cm="1">
+        <f t="array" ref="S56">IFERROR(
+    LOOKUP(2^15, SEARCH({"16","18","14"}, D56), {"16","18","14"}),
+    ""
+)</f>
+        <v>16</v>
       </c>
       <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56">
         <v>8</v>
       </c>
-      <c r="V56">
-        <v>6</v>
-      </c>
       <c r="W56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="Y56">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AA56" t="s">
         <v>16</v>
@@ -4791,41 +5105,67 @@
     </row>
     <row r="57" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>149</v>
+        <v>95</v>
+      </c>
+      <c r="C57" t="s">
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>146</v>
-      </c>
-      <c r="E57" t="s">
-        <v>151</v>
-      </c>
-      <c r="F57">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57">
         <v>1</v>
+      </c>
+      <c r="J57">
+        <v>165</v>
       </c>
       <c r="M57" t="str">
         <f>TRIM(MID(D57, FIND(",", D57)+1, FIND("/", D57)-FIND(",", D57)-1))</f>
-        <v>R7 350</v>
+        <v>i7 14650HX</v>
+      </c>
+      <c r="N57" t="str">
+        <f>_xlfn.LET(
+    _xlpm.txt, TRIM(MID(D57, FIND("/", D57)+1, LEN(D57))),
+    IFERROR(LEFT(_xlpm.txt, FIND("Ti", _xlpm.txt)+1), LEFT(_xlpm.txt, FIND(" ", _xlpm.txt&amp;" ")-1))
+)</f>
+        <v>5060</v>
+      </c>
+      <c r="O57">
+        <v>16</v>
+      </c>
+      <c r="P57" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q57">
+        <v>512</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57" t="str" cm="1">
+        <f t="array" ref="S57">IFERROR(
+    LOOKUP(2^15, SEARCH({"16","18","14"}, D57), {"16","18","14"}),
+    ""
+)</f>
+        <v>14</v>
       </c>
       <c r="U57">
+        <v>1</v>
+      </c>
+      <c r="V57">
         <v>8</v>
       </c>
-      <c r="V57">
-        <v>6</v>
-      </c>
       <c r="W57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="Y57">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA57" t="s">
         <v>16</v>
@@ -4833,7 +5173,7 @@
     </row>
     <row r="58" spans="2:27" x14ac:dyDescent="0.3">
       <c r="M58" t="e">
-        <f t="shared" ref="M58:M59" si="5">TRIM(MID(D58, FIND(",", D58)+1, FIND("/", D58)-FIND(",", D58)-1))</f>
+        <f>TRIM(MID(D58, FIND(",", D58)+1, FIND("/", D58)-FIND(",", D58)-1))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AA58" t="s">
@@ -4842,7 +5182,7 @@
     </row>
     <row r="59" spans="2:27" x14ac:dyDescent="0.3">
       <c r="M59" t="e">
-        <f t="shared" si="5"/>
+        <f>TRIM(MID(D59, FIND(",", D59)+1, FIND("/", D59)-FIND(",", D59)-1))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AA59" t="s">
@@ -4945,14 +5285,14 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y78">
-    <sortCondition ref="M1:M78"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y80">
+    <sortCondition ref="C1:C80"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{108D5653-76A3-468D-822D-5792F977922A}"/>
-    <hyperlink ref="B24" r:id="rId2" xr:uid="{671AC1F8-9822-4FFF-A6F5-FC1158DF84A7}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{AE84D4BF-8FA3-4B99-85DE-5D69AE3F3E8D}"/>
+    <hyperlink ref="B15" r:id="rId1" display="https://www.coupang.com/vp/products/8852815391?itemId=25809161282&amp;vendorItemId=92796439383" xr:uid="{108D5653-76A3-468D-822D-5792F977922A}"/>
+    <hyperlink ref="B17" r:id="rId2" display="https://www.coupang.com/vp/products/8899002151?itemId=25984595232&amp;vendorItemId=92967046664" xr:uid="{671AC1F8-9822-4FFF-A6F5-FC1158DF84A7}"/>
+    <hyperlink ref="B30" r:id="rId3" display="https://www.coupang.com/vp/products/7685542307?itemId=19025582401&amp;vendorItemId=86149803397" xr:uid="{AE84D4BF-8FA3-4B99-85DE-5D69AE3F3E8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
